--- a/artfynd/Gräsmyren artfynd.xlsx
+++ b/artfynd/Gräsmyren artfynd.xlsx
@@ -1771,59 +1771,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118963938</v>
+        <v>118963943</v>
       </c>
       <c r="B12" t="n">
-        <v>79396</v>
+        <v>91859</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>639</v>
+        <v>112</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grenlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Evernia mesomorpha</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Nyl.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gräsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460801</v>
+        <v>460585</v>
       </c>
       <c r="R12" t="n">
-        <v>6918829</v>
+        <v>6918920</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1847,12 +1836,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1861,24 +1850,8 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1895,10 +1868,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118963939</v>
+        <v>118963969</v>
       </c>
       <c r="B13" t="n">
-        <v>80433</v>
+        <v>79359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1906,21 +1879,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1930,13 +1903,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460764</v>
+        <v>460665</v>
       </c>
       <c r="R13" t="n">
-        <v>6918868</v>
+        <v>6919082</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1992,10 +1965,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118963940</v>
+        <v>118963973</v>
       </c>
       <c r="B14" t="n">
-        <v>80432</v>
+        <v>79359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,21 +1976,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2027,10 +2000,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460749</v>
+        <v>460875</v>
       </c>
       <c r="R14" t="n">
-        <v>6918861</v>
+        <v>6919134</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,12 +2030,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2089,45 +2062,56 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118963941</v>
+        <v>118963938</v>
       </c>
       <c r="B15" t="n">
-        <v>80467</v>
+        <v>79396</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>639</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Grenlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Evernia mesomorpha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Nyl.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gräsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460681</v>
+        <v>460801</v>
       </c>
       <c r="R15" t="n">
-        <v>6918870</v>
+        <v>6918829</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2154,12 +2138,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,8 +2152,24 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2186,10 +2186,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118963943</v>
+        <v>118963974</v>
       </c>
       <c r="B16" t="n">
-        <v>91859</v>
+        <v>79406</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2197,21 +2197,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>112</v>
+        <v>864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2221,13 +2221,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460585</v>
+        <v>460873</v>
       </c>
       <c r="R16" t="n">
-        <v>6918920</v>
+        <v>6919133</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2251,12 +2251,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2283,10 +2283,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118963969</v>
+        <v>118963950</v>
       </c>
       <c r="B17" t="n">
-        <v>79359</v>
+        <v>91905</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,21 +2294,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2318,13 +2318,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460665</v>
+        <v>460885</v>
       </c>
       <c r="R17" t="n">
-        <v>6919082</v>
+        <v>6918961</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2380,10 +2380,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118963973</v>
+        <v>118963946</v>
       </c>
       <c r="B18" t="n">
-        <v>79359</v>
+        <v>83173</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2391,21 +2391,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2415,13 +2415,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460875</v>
+        <v>460655</v>
       </c>
       <c r="R18" t="n">
-        <v>6919134</v>
+        <v>6918918</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118963974</v>
+        <v>118963939</v>
       </c>
       <c r="B19" t="n">
-        <v>79406</v>
+        <v>80433</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2488,21 +2488,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2512,13 +2512,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460873</v>
+        <v>460764</v>
       </c>
       <c r="R19" t="n">
-        <v>6919133</v>
+        <v>6918868</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2574,10 +2574,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118963950</v>
+        <v>118963947</v>
       </c>
       <c r="B20" t="n">
-        <v>91905</v>
+        <v>80433</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2585,21 +2585,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2609,10 +2609,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460885</v>
+        <v>460750</v>
       </c>
       <c r="R20" t="n">
-        <v>6918961</v>
+        <v>6918931</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,10 +2671,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118963946</v>
+        <v>118963970</v>
       </c>
       <c r="B21" t="n">
-        <v>83173</v>
+        <v>80433</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2682,21 +2682,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2706,13 +2706,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460655</v>
+        <v>460953</v>
       </c>
       <c r="R21" t="n">
-        <v>6918918</v>
+        <v>6919074</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2736,12 +2736,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2768,32 +2768,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118963947</v>
+        <v>118963993</v>
       </c>
       <c r="B22" t="n">
-        <v>80433</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2803,13 +2803,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>460750</v>
+        <v>461145</v>
       </c>
       <c r="R22" t="n">
-        <v>6918931</v>
+        <v>6919239</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2833,12 +2833,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2865,10 +2865,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118963970</v>
+        <v>118963945</v>
       </c>
       <c r="B23" t="n">
-        <v>80433</v>
+        <v>83307</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>460953</v>
+        <v>460588</v>
       </c>
       <c r="R23" t="n">
-        <v>6919074</v>
+        <v>6918936</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2962,32 +2962,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118963993</v>
+        <v>118963940</v>
       </c>
       <c r="B24" t="n">
-        <v>79327</v>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2997,13 +2997,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461145</v>
+        <v>460749</v>
       </c>
       <c r="R24" t="n">
-        <v>6919239</v>
+        <v>6918861</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3027,12 +3027,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3059,10 +3059,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118963945</v>
+        <v>118963951</v>
       </c>
       <c r="B25" t="n">
-        <v>83307</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3070,21 +3070,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3094,10 +3094,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>460588</v>
+        <v>460919</v>
       </c>
       <c r="R25" t="n">
-        <v>6918936</v>
+        <v>6919001</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3156,32 +3156,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118963951</v>
+        <v>118963954</v>
       </c>
       <c r="B26" t="n">
-        <v>80432</v>
+        <v>80461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>460919</v>
+        <v>460925</v>
       </c>
       <c r="R26" t="n">
-        <v>6919001</v>
+        <v>6918990</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3253,10 +3253,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118963954</v>
+        <v>118963941</v>
       </c>
       <c r="B27" t="n">
-        <v>80461</v>
+        <v>80467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3264,21 +3264,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>460925</v>
+        <v>460681</v>
       </c>
       <c r="R27" t="n">
-        <v>6918990</v>
+        <v>6918870</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4043,7 +4043,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119404939</v>
+        <v>16847432</v>
       </c>
       <c r="B35" t="n">
         <v>92208</v>
@@ -4071,24 +4071,20 @@
           <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>BÃ¶leskÃ¶len, Jmt</t>
+          <t>Gräsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>460882</v>
+        <v>460864</v>
       </c>
       <c r="R35" t="n">
-        <v>6919774</v>
+        <v>6919808</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4112,22 +4108,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2014-06-09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2014-06-09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4138,23 +4124,37 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>gransumpskog</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
+          <t>Niina Sallmén, sofia nordin</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119404947</v>
+        <v>119404939</v>
       </c>
       <c r="B36" t="n">
         <v>92208</v>
@@ -4189,17 +4189,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Holmbodarna, Jmt</t>
+          <t>BÃ¶leskÃ¶len, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461114</v>
+        <v>460882</v>
       </c>
       <c r="R36" t="n">
-        <v>6919494</v>
+        <v>6919774</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4265,10 +4265,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119404952</v>
+        <v>119404947</v>
       </c>
       <c r="B37" t="n">
-        <v>79406</v>
+        <v>92208</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4276,21 +4276,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4300,14 +4300,14 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>BÃ¶leskÃ¶len, Jmt</t>
+          <t>Holmbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>460661</v>
+        <v>461114</v>
       </c>
       <c r="R37" t="n">
-        <v>6919550</v>
+        <v>6919494</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4334,22 +4334,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4376,10 +4376,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119404940</v>
+        <v>119404952</v>
       </c>
       <c r="B38" t="n">
-        <v>91909</v>
+        <v>79406</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4387,21 +4387,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461001</v>
+        <v>460661</v>
       </c>
       <c r="R38" t="n">
-        <v>6919726</v>
+        <v>6919550</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4445,22 +4445,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4487,10 +4487,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119404949</v>
+        <v>119404935</v>
       </c>
       <c r="B39" t="n">
-        <v>83173</v>
+        <v>91909</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4498,21 +4498,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4526,10 +4526,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460710</v>
+        <v>460670</v>
       </c>
       <c r="R39" t="n">
-        <v>6919568</v>
+        <v>6919873</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4598,10 +4598,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119404957</v>
+        <v>119404940</v>
       </c>
       <c r="B40" t="n">
-        <v>92097</v>
+        <v>91909</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4609,21 +4609,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1588</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460989</v>
+        <v>461001</v>
       </c>
       <c r="R40" t="n">
-        <v>6919623</v>
+        <v>6919726</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4667,22 +4667,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4709,32 +4709,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119404953</v>
+        <v>119404937</v>
       </c>
       <c r="B41" t="n">
-        <v>80432</v>
+        <v>91923</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4748,13 +4748,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460702</v>
+        <v>460758</v>
       </c>
       <c r="R41" t="n">
-        <v>6919526</v>
+        <v>6919790</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4778,22 +4778,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4820,10 +4820,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119404955</v>
+        <v>119404934</v>
       </c>
       <c r="B42" t="n">
-        <v>80432</v>
+        <v>83173</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4831,21 +4831,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4859,10 +4859,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>460923</v>
+        <v>460610</v>
       </c>
       <c r="R42" t="n">
-        <v>6919611</v>
+        <v>6919826</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4889,22 +4889,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4931,10 +4931,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119404958</v>
+        <v>119404949</v>
       </c>
       <c r="B43" t="n">
-        <v>80432</v>
+        <v>83173</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4942,21 +4942,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4966,14 +4966,14 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Holmbodarna, Jmt</t>
+          <t>BÃ¶leskÃ¶len, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461136</v>
+        <v>460710</v>
       </c>
       <c r="R43" t="n">
-        <v>6919436</v>
+        <v>6919568</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5000,22 +5000,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5042,10 +5042,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>16847432</v>
+        <v>119404957</v>
       </c>
       <c r="B44" t="n">
-        <v>92208</v>
+        <v>92097</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5053,34 +5053,38 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>1588</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gräsmyren, Jmt</t>
+          <t>BÃ¶leskÃ¶len, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>460864</v>
+        <v>460989</v>
       </c>
       <c r="R44" t="n">
-        <v>6919808</v>
+        <v>6919623</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5107,12 +5111,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2014-06-09</t>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2014-06-09</t>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5123,62 +5137,48 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>gransumpskog</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Niina Sallmén, sofia nordin</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119404931</v>
+        <v>119404933</v>
       </c>
       <c r="B45" t="n">
-        <v>92208</v>
+        <v>92283</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>2063</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461098</v>
+        <v>461050</v>
       </c>
       <c r="R45" t="n">
-        <v>6919963</v>
+        <v>6919893</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5264,10 +5264,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119404928</v>
+        <v>119404953</v>
       </c>
       <c r="B46" t="n">
-        <v>91909</v>
+        <v>80432</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5275,21 +5275,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5303,13 +5303,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461117</v>
+        <v>460702</v>
       </c>
       <c r="R46" t="n">
-        <v>6919946</v>
+        <v>6919526</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5333,22 +5333,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5375,10 +5375,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119404935</v>
+        <v>119404955</v>
       </c>
       <c r="B47" t="n">
-        <v>91909</v>
+        <v>80432</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5386,21 +5386,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5414,10 +5414,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>460670</v>
+        <v>460923</v>
       </c>
       <c r="R47" t="n">
-        <v>6919873</v>
+        <v>6919611</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5444,22 +5444,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5486,32 +5486,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119404937</v>
+        <v>119404958</v>
       </c>
       <c r="B48" t="n">
-        <v>91923</v>
+        <v>80432</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5521,14 +5521,14 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>BÃ¶leskÃ¶len, Jmt</t>
+          <t>Holmbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>460758</v>
+        <v>461136</v>
       </c>
       <c r="R48" t="n">
-        <v>6919790</v>
+        <v>6919436</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5555,22 +5555,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5597,10 +5597,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119404934</v>
+        <v>119404931</v>
       </c>
       <c r="B49" t="n">
-        <v>83173</v>
+        <v>92208</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5608,21 +5608,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5636,13 +5636,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>460610</v>
+        <v>461098</v>
       </c>
       <c r="R49" t="n">
-        <v>6919826</v>
+        <v>6919963</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5666,22 +5666,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5708,32 +5708,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119404933</v>
+        <v>119404928</v>
       </c>
       <c r="B50" t="n">
-        <v>92283</v>
+        <v>91909</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2063</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5747,13 +5747,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461050</v>
+        <v>461117</v>
       </c>
       <c r="R50" t="n">
-        <v>6919893</v>
+        <v>6919946</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -10424,10 +10424,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118963929</v>
+        <v>16847440</v>
       </c>
       <c r="B94" t="n">
-        <v>79406</v>
+        <v>92208</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10435,21 +10435,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10459,10 +10459,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>461548</v>
+        <v>461347</v>
       </c>
       <c r="R94" t="n">
-        <v>6919709</v>
+        <v>6919896</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10489,12 +10489,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2014-06-11</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2014-06-11</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10505,26 +10505,40 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>bäckgranskog</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
+          <t>Niina Sallmén, sofia nordin</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119404945</v>
+        <v>119404927</v>
       </c>
       <c r="B95" t="n">
-        <v>83173</v>
+        <v>92208</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10532,21 +10546,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -10556,14 +10570,14 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Holmbodarna, Jmt</t>
+          <t>BÃ¶leskÃ¶len, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>461390</v>
+        <v>461407</v>
       </c>
       <c r="R95" t="n">
-        <v>6919578</v>
+        <v>6919862</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10590,22 +10604,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10632,10 +10646,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118963931</v>
+        <v>118963929</v>
       </c>
       <c r="B96" t="n">
-        <v>80433</v>
+        <v>79406</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10643,21 +10657,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10667,13 +10681,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>461576</v>
+        <v>461548</v>
       </c>
       <c r="R96" t="n">
-        <v>6919636</v>
+        <v>6919709</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10729,10 +10743,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119404943</v>
+        <v>119404945</v>
       </c>
       <c r="B97" t="n">
-        <v>80433</v>
+        <v>83173</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10740,21 +10754,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -10768,13 +10782,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>461489</v>
+        <v>461390</v>
       </c>
       <c r="R97" t="n">
-        <v>6919561</v>
+        <v>6919578</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10803,7 +10817,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10813,7 +10827,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10840,10 +10854,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118963937</v>
+        <v>118963931</v>
       </c>
       <c r="B98" t="n">
-        <v>83307</v>
+        <v>80433</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10851,21 +10865,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10875,13 +10889,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>461580</v>
+        <v>461576</v>
       </c>
       <c r="R98" t="n">
-        <v>6919459</v>
+        <v>6919636</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10937,10 +10951,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118963935</v>
+        <v>119096819</v>
       </c>
       <c r="B99" t="n">
-        <v>80432</v>
+        <v>80433</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10948,37 +10962,41 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Gräsmyren, Jmt</t>
+          <t>Holmbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>461607</v>
+        <v>461790</v>
       </c>
       <c r="R99" t="n">
-        <v>6919437</v>
+        <v>6919817</v>
       </c>
       <c r="S99" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11005,9 +11023,19 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11022,22 +11050,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119404944</v>
+        <v>119404943</v>
       </c>
       <c r="B100" t="n">
-        <v>80432</v>
+        <v>80433</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11045,21 +11073,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -11145,32 +11173,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118963936</v>
+        <v>118963937</v>
       </c>
       <c r="B101" t="n">
-        <v>79583</v>
+        <v>83307</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6459</v>
+        <v>6440</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11180,13 +11208,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>461583</v>
+        <v>461580</v>
       </c>
       <c r="R101" t="n">
         <v>6919459</v>
       </c>
       <c r="S101" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11242,32 +11270,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118963934</v>
+        <v>118963935</v>
       </c>
       <c r="B102" t="n">
-        <v>80392</v>
+        <v>80432</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11277,13 +11305,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>461608</v>
+        <v>461607</v>
       </c>
       <c r="R102" t="n">
-        <v>6919439</v>
+        <v>6919437</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11339,10 +11367,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>16847440</v>
+        <v>119096818</v>
       </c>
       <c r="B103" t="n">
-        <v>92208</v>
+        <v>80432</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11350,34 +11378,38 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Gräsmyren, Jmt</t>
+          <t>Holmbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>461347</v>
+        <v>461806</v>
       </c>
       <c r="R103" t="n">
-        <v>6919896</v>
+        <v>6919828</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11404,12 +11436,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2014-06-11</t>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2014-06-11</t>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11420,40 +11462,26 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>bäckgranskog</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Niina Sallmén, sofia nordin</t>
-        </is>
-      </c>
-      <c r="AY103" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119404927</v>
+        <v>119404944</v>
       </c>
       <c r="B104" t="n">
-        <v>92208</v>
+        <v>80432</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11461,21 +11489,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -11485,17 +11513,17 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>BÃ¶leskÃ¶len, Jmt</t>
+          <t>Holmbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>461407</v>
+        <v>461489</v>
       </c>
       <c r="R104" t="n">
-        <v>6919862</v>
+        <v>6919561</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11519,22 +11547,22 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11561,32 +11589,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>16847438</v>
+        <v>118963936</v>
       </c>
       <c r="B105" t="n">
-        <v>91909</v>
+        <v>79583</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>6459</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11596,13 +11624,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>461246</v>
+        <v>461583</v>
       </c>
       <c r="R105" t="n">
-        <v>6919918</v>
+        <v>6919459</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11626,12 +11654,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2014-06-11</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2014-06-11</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11642,82 +11670,64 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
-      </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>bäckgranskog</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Niina Sallmén, sofia nordin</t>
-        </is>
-      </c>
-      <c r="AY105" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119404918</v>
+        <v>118963934</v>
       </c>
       <c r="B106" t="n">
-        <v>92097</v>
+        <v>80392</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1588</v>
+        <v>229497</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>BÃ¶leskÃ¶len, Jmt</t>
+          <t>Gräsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>461661</v>
+        <v>461608</v>
       </c>
       <c r="R106" t="n">
-        <v>6920050</v>
+        <v>6919439</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11741,22 +11751,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11771,22 +11771,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119096819</v>
+        <v>16847438</v>
       </c>
       <c r="B107" t="n">
-        <v>80433</v>
+        <v>91909</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11794,41 +11794,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Holmbodarna, Jmt</t>
+          <t>Gräsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>461790</v>
+        <v>461246</v>
       </c>
       <c r="R107" t="n">
-        <v>6919817</v>
+        <v>6919918</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11852,22 +11848,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2014-06-11</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2014-06-11</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11878,26 +11864,40 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>bäckgranskog</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr"/>
+          <t>Niina Sallmén, sofia nordin</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119096818</v>
+        <v>119404918</v>
       </c>
       <c r="B108" t="n">
-        <v>80432</v>
+        <v>92097</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11905,21 +11905,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>1588</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -11929,17 +11929,17 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Holmbodarna, Jmt</t>
+          <t>BÃ¶leskÃ¶len, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>461806</v>
+        <v>461661</v>
       </c>
       <c r="R108" t="n">
-        <v>6919828</v>
+        <v>6920050</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11963,22 +11963,22 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11993,12 +11993,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -14659,10 +14659,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>16847442</v>
+        <v>119404925</v>
       </c>
       <c r="B133" t="n">
-        <v>80433</v>
+        <v>91909</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14670,34 +14670,38 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Gräsmyren, Jmt</t>
+          <t>Holmbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>461948</v>
+        <v>462116</v>
       </c>
       <c r="R133" t="n">
-        <v>6919472</v>
+        <v>6919863</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14724,12 +14728,22 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2014-06-11</t>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2014-06-11</t>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14740,37 +14754,23 @@
       </c>
       <c r="AG133" t="b">
         <v>0</v>
-      </c>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>granskog</t>
-        </is>
-      </c>
-      <c r="AO133" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Niina Sallmén, sofia nordin</t>
-        </is>
-      </c>
-      <c r="AY133" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>119096811</v>
+        <v>16847442</v>
       </c>
       <c r="B134" t="n">
         <v>80433</v>
@@ -14798,24 +14798,20 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Holmbodarna, Jmt</t>
+          <t>Gräsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>461980</v>
+        <v>461948</v>
       </c>
       <c r="R134" t="n">
-        <v>6919468</v>
+        <v>6919472</v>
       </c>
       <c r="S134" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14839,22 +14835,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
-        </is>
-      </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>11:57</t>
+          <t>2014-06-11</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>11:57</t>
+          <t>2014-06-11</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14865,23 +14851,37 @@
       </c>
       <c r="AG134" t="b">
         <v>0</v>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>granskog</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
-        </is>
-      </c>
-      <c r="AY134" t="inlineStr"/>
+          <t>Niina Sallmén, sofia nordin</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119096821</v>
+        <v>119096811</v>
       </c>
       <c r="B135" t="n">
         <v>80433</v>
@@ -14920,10 +14920,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>461939</v>
+        <v>461980</v>
       </c>
       <c r="R135" t="n">
-        <v>6919461</v>
+        <v>6919468</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -14955,7 +14955,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14965,7 +14965,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14992,10 +14992,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119096808</v>
+        <v>119096821</v>
       </c>
       <c r="B136" t="n">
-        <v>80432</v>
+        <v>80433</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15003,21 +15003,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -15031,10 +15031,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>462045</v>
+        <v>461939</v>
       </c>
       <c r="R136" t="n">
-        <v>6919451</v>
+        <v>6919461</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -15066,7 +15066,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15103,7 +15103,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119096810</v>
+        <v>119096808</v>
       </c>
       <c r="B137" t="n">
         <v>80432</v>
@@ -15142,10 +15142,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>461991</v>
+        <v>462045</v>
       </c>
       <c r="R137" t="n">
-        <v>6919469</v>
+        <v>6919451</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -15177,7 +15177,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15187,7 +15187,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15214,7 +15214,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119096813</v>
+        <v>119096810</v>
       </c>
       <c r="B138" t="n">
         <v>80432</v>
@@ -15253,10 +15253,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>461975</v>
+        <v>461991</v>
       </c>
       <c r="R138" t="n">
-        <v>6919476</v>
+        <v>6919469</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -15288,7 +15288,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15298,7 +15298,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15325,7 +15325,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119096817</v>
+        <v>119096813</v>
       </c>
       <c r="B139" t="n">
         <v>80432</v>
@@ -15364,13 +15364,13 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>461822</v>
+        <v>461975</v>
       </c>
       <c r="R139" t="n">
-        <v>6919735</v>
+        <v>6919476</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15436,7 +15436,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119096820</v>
+        <v>119096817</v>
       </c>
       <c r="B140" t="n">
         <v>80432</v>
@@ -15475,10 +15475,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>461927</v>
+        <v>461822</v>
       </c>
       <c r="R140" t="n">
-        <v>6919452</v>
+        <v>6919735</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15520,7 +15520,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15547,32 +15547,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119096815</v>
+        <v>119096820</v>
       </c>
       <c r="B141" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -15586,13 +15586,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>461981</v>
+        <v>461927</v>
       </c>
       <c r="R141" t="n">
-        <v>6919490</v>
+        <v>6919452</v>
       </c>
       <c r="S141" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15631,7 +15631,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15658,10 +15658,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119096814</v>
+        <v>119096815</v>
       </c>
       <c r="B142" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15669,21 +15669,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -15697,10 +15697,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>461980</v>
+        <v>461981</v>
       </c>
       <c r="R142" t="n">
-        <v>6919488</v>
+        <v>6919490</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -15769,32 +15769,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119404922</v>
+        <v>119096814</v>
       </c>
       <c r="B143" t="n">
-        <v>99116</v>
+        <v>80467</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>620</v>
+        <v>6463</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -15808,10 +15808,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>461926</v>
+        <v>461980</v>
       </c>
       <c r="R143" t="n">
-        <v>6919931</v>
+        <v>6919488</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -15838,22 +15838,22 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15868,22 +15868,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119404924</v>
+        <v>119404922</v>
       </c>
       <c r="B144" t="n">
-        <v>92208</v>
+        <v>99116</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15891,21 +15891,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>658</v>
+        <v>620</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -15919,10 +15919,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>461981</v>
+        <v>461926</v>
       </c>
       <c r="R144" t="n">
-        <v>6919934</v>
+        <v>6919931</v>
       </c>
       <c r="S144" t="n">
         <v>5</v>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15964,7 +15964,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15991,10 +15991,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119404923</v>
+        <v>119404924</v>
       </c>
       <c r="B145" t="n">
-        <v>91909</v>
+        <v>92208</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16002,21 +16002,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -16030,13 +16030,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>461978</v>
+        <v>461981</v>
       </c>
       <c r="R145" t="n">
-        <v>6919932</v>
+        <v>6919934</v>
       </c>
       <c r="S145" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119404925</v>
+        <v>119404923</v>
       </c>
       <c r="B146" t="n">
         <v>91909</v>
@@ -16141,10 +16141,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>462116</v>
+        <v>461978</v>
       </c>
       <c r="R146" t="n">
-        <v>6919863</v>
+        <v>6919932</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16176,7 +16176,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16186,7 +16186,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD146" t="b">
